--- a/NBFC-MF/Borrowers/Th_Memcha_Weekly.xlsx
+++ b/NBFC-MF/Borrowers/Th_Memcha_Weekly.xlsx
@@ -1138,42 +1138,44 @@
       </c>
       <c r="K12" s="9">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A13" s="19"/>
-      <c r="B13" s="23" t="str">
+      <c r="A13" s="19">
+        <v>46286</v>
+      </c>
+      <c r="B13" s="23">
         <f t="shared" si="3"/>
-        <v/>
+        <v>12</v>
       </c>
       <c r="C13" s="20"/>
-      <c r="D13" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E13" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F13" s="21" t="str">
+      <c r="D13" s="21">
+        <f t="shared" si="0"/>
+        <v>700</v>
+      </c>
+      <c r="E13" s="21">
+        <f t="shared" si="1"/>
+        <v>78.608528268940589</v>
+      </c>
+      <c r="F13" s="21">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="G13" s="21" t="str">
+        <v>621.39147173105937</v>
+      </c>
+      <c r="G13" s="21">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="H13" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+        <v>3298.927950640365</v>
+      </c>
+      <c r="H13" s="21">
+        <f t="shared" si="2"/>
+        <v>6701.0720493596345</v>
       </c>
       <c r="J13" s="24" t="s">
         <v>21</v>
       </c>
       <c r="K13" s="11">
         <f>(K10*K9)-K9*K12</f>
-        <v>4200</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
@@ -1208,7 +1210,7 @@
       </c>
       <c r="K14" s="11">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>3920.3194223714245</v>
+        <v>3298.927950640365</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -1243,7 +1245,7 @@
       </c>
       <c r="K15" s="13">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>6079.6805776285755</v>
+        <v>6701.0720493596345</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">

--- a/NBFC-MF/Borrowers/Th_Memcha_Weekly.xlsx
+++ b/NBFC-MF/Borrowers/Th_Memcha_Weekly.xlsx
@@ -1138,7 +1138,7 @@
       </c>
       <c r="K12" s="9">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
@@ -1175,42 +1175,44 @@
       </c>
       <c r="K13" s="11">
         <f>(K10*K9)-K9*K12</f>
-        <v>3500</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A14" s="2"/>
-      <c r="B14" s="22" t="str">
+      <c r="A14" s="2">
+        <v>46290</v>
+      </c>
+      <c r="B14" s="22">
         <f t="shared" si="3"/>
-        <v/>
+        <v>13</v>
       </c>
       <c r="C14" s="3"/>
-      <c r="D14" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E14" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F14" s="1" t="str">
+      <c r="D14" s="1">
+        <f t="shared" si="0"/>
+        <v>700</v>
+      </c>
+      <c r="E14" s="1">
+        <f t="shared" si="1"/>
+        <v>66.148658597886595</v>
+      </c>
+      <c r="F14" s="1">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="G14" s="1" t="str">
+        <v>633.85134140211335</v>
+      </c>
+      <c r="G14" s="1">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="H14" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+        <v>2665.0766092382519</v>
+      </c>
+      <c r="H14" s="1">
+        <f t="shared" si="2"/>
+        <v>7334.9233907617481</v>
       </c>
       <c r="J14" s="10" t="s">
         <v>22</v>
       </c>
       <c r="K14" s="11">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>3298.927950640365</v>
+        <v>2665.0766092382519</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -1245,7 +1247,7 @@
       </c>
       <c r="K15" s="13">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>6701.0720493596345</v>
+        <v>7334.9233907617481</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">

--- a/NBFC-MF/Borrowers/Th_Memcha_Weekly.xlsx
+++ b/NBFC-MF/Borrowers/Th_Memcha_Weekly.xlsx
@@ -1138,7 +1138,7 @@
       </c>
       <c r="K12" s="9">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="K13" s="11">
         <f>(K10*K9)-K9*K12</f>
-        <v>2800</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
@@ -1212,70 +1212,74 @@
       </c>
       <c r="K14" s="11">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>2665.0766092382519</v>
+        <v>1358.9899483407528</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="19"/>
-      <c r="B15" s="23" t="str">
+      <c r="A15" s="19">
+        <v>46305</v>
+      </c>
+      <c r="B15" s="23">
         <f t="shared" si="3"/>
-        <v/>
+        <v>14</v>
       </c>
       <c r="C15" s="20"/>
-      <c r="D15" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E15" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F15" s="21" t="str">
+      <c r="D15" s="21">
+        <f t="shared" si="0"/>
+        <v>700</v>
+      </c>
+      <c r="E15" s="21">
+        <f t="shared" si="1"/>
+        <v>53.438949076621675</v>
+      </c>
+      <c r="F15" s="21">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="G15" s="21" t="str">
+        <v>646.56105092337828</v>
+      </c>
+      <c r="G15" s="21">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="H15" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+        <v>2018.5155583148735</v>
+      </c>
+      <c r="H15" s="21">
+        <f t="shared" si="2"/>
+        <v>7981.4844416851265</v>
       </c>
       <c r="J15" s="12" t="s">
         <v>5</v>
       </c>
       <c r="K15" s="13">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>7334.9233907617481</v>
+        <v>8641.0100516592465</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A16" s="2"/>
-      <c r="B16" s="22" t="str">
+      <c r="A16" s="2">
+        <v>46305</v>
+      </c>
+      <c r="B16" s="22">
         <f t="shared" si="3"/>
-        <v/>
+        <v>15</v>
       </c>
       <c r="C16" s="3"/>
-      <c r="D16" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E16" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F16" s="1" t="str">
+      <c r="D16" s="1">
+        <f t="shared" si="0"/>
+        <v>700</v>
+      </c>
+      <c r="E16" s="1">
+        <f t="shared" si="1"/>
+        <v>40.474390025879359</v>
+      </c>
+      <c r="F16" s="1">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="G16" s="1" t="str">
+        <v>659.5256099741207</v>
+      </c>
+      <c r="G16" s="1">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="H16" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+        <v>1358.9899483407528</v>
+      </c>
+      <c r="H16" s="1">
+        <f t="shared" si="2"/>
+        <v>8641.0100516592465</v>
       </c>
       <c r="J16" s="15" t="s">
         <v>18</v>
